--- a/DataTables/DetailText/剧情/024_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/024_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30364819-8445-4715-B88B-31B0B6D9A68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33279BED-B627-4C96-85D3-8C654D02C07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19395" yWindow="5745" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="65">
   <si>
     <t>LineIndex</t>
   </si>
@@ -308,7 +297,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -322,7 +311,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -343,7 +332,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -517,7 +506,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -796,25 +785,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultColWidth="19.5" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="19.46484375" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="22" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="22" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>45</v>
       </c>
@@ -876,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="22" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="22" customFormat="1">
       <c r="A2" s="11" t="s">
         <v>15</v>
       </c>
@@ -1000,14 +989,14 @@
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="92.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="92.3984375" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1255,7 +1244,9 @@
         <v>37</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="G11" s="3"/>
       <c r="H11" s="14" t="s">
         <v>44</v>

--- a/DataTables/DetailText/剧情/024_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/024_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33279BED-B627-4C96-85D3-8C654D02C07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B91D04B-B3B1-4F6D-A9F4-F2AA0001BD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="67">
   <si>
     <t>LineIndex</t>
   </si>
@@ -287,6 +287,14 @@
   <si>
     <t>Music</t>
     <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/black.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>收入一两白银</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -891,7 +899,9 @@
       <c r="M2" s="23"/>
       <c r="N2" s="24"/>
       <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
+      <c r="P2" s="24">
+        <v>1000</v>
+      </c>
       <c r="Q2" s="24"/>
       <c r="R2" s="25"/>
       <c r="S2" s="25" t="b">
@@ -986,7 +996,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
@@ -1298,15 +1308,15 @@
       <c r="B14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="2"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="2" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="I14" s="1"/>
     </row>
@@ -1315,19 +1325,17 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>8</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="2"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="G15" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="H15" s="14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I15" s="1"/>
     </row>
@@ -1338,17 +1346,17 @@
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>19</v>
+      <c r="C16" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="14" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I16" s="1"/>
     </row>
@@ -1359,17 +1367,17 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="14" t="s">
-        <v>29</v>
+      <c r="C17" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I17" s="1"/>
     </row>
@@ -1380,17 +1388,17 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>19</v>
+      <c r="C18" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18" s="1"/>
     </row>
@@ -1401,30 +1409,51 @@
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>29</v>
+      <c r="C19" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="1"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="2"/>
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+      <c r="H20" s="14" t="s">
+        <v>35</v>
+      </c>
       <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="1"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/024_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/024_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B91D04B-B3B1-4F6D-A9F4-F2AA0001BD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D38D103-5425-4948-AAFC-B11D3145FED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="66">
   <si>
     <t>LineIndex</t>
   </si>
@@ -287,10 +287,6 @@
   <si>
     <t>Music</t>
     <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>res://Assets/Background/black.png</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>收入一两白银</t>
@@ -1312,11 +1308,9 @@
       <c r="D14" s="7"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="2"/>
+      <c r="H14" s="14" t="s">
         <v>65</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>66</v>
       </c>
       <c r="I14" s="1"/>
     </row>
@@ -1331,9 +1325,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="G15" s="2"/>
       <c r="H15" s="14" t="s">
         <v>28</v>
       </c>

--- a/DataTables/DetailText/剧情/024_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/024_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D38D103-5425-4948-AAFC-B11D3145FED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8886FBCE-DA5D-473F-9687-AB57EAE8B0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -133,10 +144,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>金姨妈</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>李大夫，你叫我来是什么事儿啊？</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -190,10 +197,6 @@
   </si>
   <si>
     <t>少夫人你有什么主意呀？快说快说！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>明日你让金姨妈来一趟，如此这般….</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -292,6 +295,14 @@
     <t>收入一两白银</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>郭妈妈</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>明日你让郭妈妈来一趟，如此这般….</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -301,7 +312,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -315,7 +326,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -336,7 +347,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -510,7 +521,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -789,78 +800,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultColWidth="19.46484375" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="19.5" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.1328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="22" customFormat="1">
+    <row r="1" spans="1:20" s="22" customFormat="1" ht="18">
       <c r="A1" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="E1" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="F1" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="H1" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="I1" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="J1" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="K1" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="L1" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="M1" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="N1" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="O1" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="P1" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="R1" s="20" t="s">
         <v>60</v>
-      </c>
-      <c r="Q1" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="R1" s="20" t="s">
-        <v>62</v>
       </c>
       <c r="S1" s="21" t="s">
         <v>11</v>
@@ -869,7 +880,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="22" customFormat="1">
+    <row r="2" spans="1:20" s="22" customFormat="1" ht="18">
       <c r="A2" s="11" t="s">
         <v>15</v>
       </c>
@@ -887,7 +898,7 @@
         <v>17</v>
       </c>
       <c r="K2" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L2" s="24" t="s">
         <v>13</v>
@@ -995,14 +1006,14 @@
   <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="92.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="92.375" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1032,7 +1043,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1089,10 +1100,10 @@
         <v>6</v>
       </c>
       <c r="C4" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="7"/>
@@ -1121,7 +1132,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1133,16 +1144,16 @@
         <v>6</v>
       </c>
       <c r="C6" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -1188,7 +1199,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -1200,16 +1211,16 @@
         <v>6</v>
       </c>
       <c r="C9" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I9" s="1"/>
     </row>
@@ -1228,11 +1239,11 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I10" s="1"/>
     </row>
@@ -1244,18 +1255,18 @@
         <v>6</v>
       </c>
       <c r="C11" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="14" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="I11" s="1"/>
     </row>
@@ -1272,7 +1283,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I12" s="1"/>
     </row>
@@ -1310,7 +1321,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="2"/>
       <c r="H14" s="14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I14" s="1"/>
     </row>
@@ -1339,7 +1350,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
@@ -1348,7 +1359,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I16" s="1"/>
     </row>
@@ -1369,7 +1380,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I17" s="1"/>
     </row>
@@ -1381,7 +1392,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>8</v>
@@ -1390,7 +1401,7 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I18" s="1"/>
     </row>
@@ -1411,7 +1422,7 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" s="1"/>
     </row>
@@ -1423,7 +1434,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>8</v>
@@ -1432,7 +1443,7 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I20" s="1"/>
     </row>
